--- a/output/pdf_financials_xlsx/MEC.xlsx
+++ b/output/pdf_financials_xlsx/MEC.xlsx
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.070115</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.322244</v>
       </c>
     </row>
     <row r="93">
@@ -2501,7 +2501,7 @@
         <v>-0.525026</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>-1.776794</v>
+        <v>-1.885686</v>
       </c>
     </row>
     <row r="119">
@@ -3311,7 +3311,11 @@
           <t>Reserve 11</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3757,7 +3761,11 @@
           <t>Deposits for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MEC.xlsx
+++ b/output/pdf_financials_xlsx/MEC.xlsx
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.027784</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.060522</v>
       </c>
     </row>
     <row r="13">
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.190288</v>
+        <v>-2.218072</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.879459</v>
+        <v>-4.939981</v>
       </c>
     </row>
     <row r="28">
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.190288</v>
+        <v>-2.218072</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.879459</v>
+        <v>-4.939981</v>
       </c>
     </row>
     <row r="30">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">

--- a/output/pdf_financials_xlsx/MEC.xlsx
+++ b/output/pdf_financials_xlsx/MEC.xlsx
@@ -480,10 +480,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -498,10 +496,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -516,10 +512,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -534,16 +528,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.306146</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.171994</v>
+        <v>0.235894</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.342938</v>
+        <v>0.411338</v>
       </c>
     </row>
     <row r="8">
@@ -552,10 +544,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -570,10 +560,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.042</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0.022279</v>
@@ -588,16 +576,14 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.348146</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.194273</v>
+        <v>0.258173</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.825482</v>
+        <v>0.893882</v>
       </c>
     </row>
     <row r="11">
@@ -606,16 +592,14 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.348146</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.194273</v>
+        <v>-0.258173</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.825482</v>
+        <v>-0.893882</v>
       </c>
     </row>
     <row r="12">
@@ -624,10 +608,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.027784</v>
@@ -642,10 +624,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -660,10 +640,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -678,10 +656,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -696,10 +672,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>0.8186059999999999</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-2.190288</v>
@@ -714,10 +688,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -776,10 +748,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>0.8186059999999999</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-2.190288</v>
@@ -794,10 +764,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -812,10 +780,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -882,13 +848,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>39.218149</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>31.289829</v>
+        <v>33.204778</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>81.32431699999999</v>
@@ -900,10 +864,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>0.8186059999999999</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-2.218072</v>
@@ -918,10 +880,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -936,10 +896,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>0.8186059999999999</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-2.218072</v>
@@ -976,10 +934,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -1023,10 +979,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>1.598575</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>3.368699</v>
@@ -1041,10 +995,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -1059,10 +1011,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>1.598575</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>3.368699</v>
@@ -1077,10 +1027,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
@@ -1095,10 +1043,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -1113,10 +1059,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -1131,10 +1075,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
@@ -1149,10 +1091,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0</v>
@@ -1167,10 +1107,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -1185,10 +1123,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -1203,10 +1139,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -1221,10 +1155,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -1239,10 +1171,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -1257,10 +1187,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -1275,10 +1203,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.017675</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.344269</v>
@@ -1293,10 +1219,8 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>1.61625</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>3.712968</v>
@@ -1311,10 +1235,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
@@ -1329,10 +1251,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
@@ -1347,10 +1267,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
@@ -1365,10 +1283,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
@@ -1383,10 +1299,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
@@ -1423,10 +1337,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -1441,10 +1353,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>0</v>
@@ -1459,10 +1369,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>6.498554</v>
@@ -1477,10 +1385,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0</v>
@@ -1495,10 +1401,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -1513,10 +1417,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0</v>
@@ -1531,10 +1433,8 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>6.498554</v>
@@ -1549,10 +1449,8 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>1.61625</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>10.211522</v>
@@ -1567,16 +1465,14 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.182656</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.258443</v>
       </c>
     </row>
     <row r="65">
@@ -1585,10 +1481,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0</v>
@@ -1603,10 +1497,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -1621,16 +1513,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.064372</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.053376</v>
       </c>
     </row>
     <row r="68">
@@ -1639,10 +1529,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.031584</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.247028</v>
@@ -1657,10 +1545,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0</v>
@@ -1675,10 +1561,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -1693,10 +1577,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -1711,10 +1593,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0</v>
@@ -1729,10 +1609,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>0</v>
@@ -1747,10 +1625,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0</v>
@@ -1765,10 +1641,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0.396234</v>
@@ -1783,10 +1657,8 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>0.031584</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>0.643262</v>
@@ -1801,10 +1673,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -1819,10 +1689,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -1837,10 +1705,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -1877,10 +1743,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>0</v>
@@ -1895,10 +1759,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>0</v>
@@ -1913,10 +1775,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>0</v>
@@ -1931,10 +1791,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0</v>
@@ -1949,10 +1807,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0</v>
@@ -1967,10 +1823,8 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>0</v>
@@ -1985,10 +1839,8 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0.031584</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>0.643262</v>
@@ -2003,10 +1855,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>4.861202</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>14.09067</v>
@@ -2021,10 +1871,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0</v>
@@ -2039,10 +1887,8 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-3.812237</v>
       </c>
       <c r="C90" s="3" t="n">
         <v>-6.002525</v>
@@ -2057,10 +1903,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -2075,10 +1919,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0.535701</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>1.070115</v>
@@ -2093,10 +1935,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>0</v>
@@ -2111,10 +1951,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>1.584666</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>9.56826</v>
@@ -2129,10 +1967,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>0</v>
@@ -2147,10 +1983,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>1.584666</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>9.56826</v>
@@ -2165,10 +1999,8 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.9804584686774942</v>
       </c>
       <c r="C97" s="3" t="n">
         <v>0.9370062562662059</v>
@@ -2793,7 +2625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3027,10 +2859,8 @@
           <t>CurrentAssets</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="5" t="n">
+        <v>1.61625</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>3.712968</v>
@@ -3093,10 +2923,8 @@
           <t>TotalAssets</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="5" t="n">
+        <v>1.61625</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>10.211522</v>
@@ -3219,10 +3047,8 @@
           <t>CurrentLiabilities</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="5" t="n">
+        <v>0.031584</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.643262</v>
@@ -3349,10 +3175,8 @@
           <t>RetainedEarnings</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="5" t="n">
+        <v>-3.812237</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>-6.002525</v>
@@ -3382,10 +3206,8 @@
           <t>StockholdersEquity</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E18" s="5" t="n">
+        <v>1.584666</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>9.56826</v>
@@ -3415,10 +3237,8 @@
           <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E19" s="5" t="n">
+        <v>1.61625</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>10.211522</v>
@@ -3430,141 +3250,151 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Current assets</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>December 31, 2025 December</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>1.598575</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>3.368699</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Prepaids 8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.017675</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-2.190288</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-4.879459</v>
+        <v>0.344269</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Recovery of flow through share premium</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Exploration and evaluation assets 5</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-0.393798</v>
+      <c r="F22" s="5" t="n">
+        <v>6.498554</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>1.315969</v>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.031584</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.247028</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shares issued for consulting fees</t>
+          <t>Flow-through premium liability 7</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -3573,108 +3403,110 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.1535</v>
+      <c r="F24" s="5" t="n">
+        <v>0.396234</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Share capital 6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>4.861202</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.586429</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0.634576</v>
+        <v>14.09067</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Account payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0.00205</v>
+          <t>Commitment to issue shares 5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.09055100000000001</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.032001</v>
+        <v>0.41</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prepaids</t>
+          <t>Reserve 6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.012497</v>
+        <v>0.535701</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-0.326594</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.224855</v>
+        <v>1.070115</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -3683,33 +3515,23 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other receivable</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>December 31, 2025 December</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.051638</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="29">
@@ -3720,17 +3542,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Total cash used in operating activities</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3739,10 +3561,10 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-1.839902</v>
+        <v>-2.190288</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-2.963994</v>
+        <v>-4.879459</v>
       </c>
     </row>
     <row r="30">
@@ -3753,19 +3575,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Deposits for exploration and evaluation expenditures</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Recovery of flow through share premium</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -3777,7 +3595,7 @@
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.108892</v>
+        <v>-0.393798</v>
       </c>
     </row>
     <row r="31">
@@ -3788,12 +3606,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
+          <t>Impairment of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3806,11 +3624,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>-0.525026</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-3.092763</v>
+        <v>1.315969</v>
       </c>
     </row>
     <row r="32">
@@ -3821,12 +3641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Acquisition of Nucleus - transaction costs</t>
+          <t>Shares issued for consulting fees</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -3841,7 +3661,7 @@
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.042873</v>
+        <v>0.1535</v>
       </c>
     </row>
     <row r="33">
@@ -3852,17 +3672,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Total cash used in investing activities</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3871,10 +3691,10 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.525026</v>
+        <v>0.586429</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-3.244528</v>
+        <v>0.634576</v>
       </c>
     </row>
     <row r="34">
@@ -3885,27 +3705,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shares issued on warrant exercise</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Account payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.00205</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.697112</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09055100000000001</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.032001</v>
       </c>
     </row>
     <row r="35">
@@ -3916,25 +3736,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shares issued for private placement financing</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaids</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.012497</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>3.55295</v>
+        <v>-0.326594</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>3.584136</v>
+        <v>0.224855</v>
       </c>
     </row>
     <row r="36">
@@ -3945,17 +3767,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
+          <t>Other receivable</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3963,11 +3785,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>-0.11501</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.207407</v>
+        <v>-0.051638</v>
       </c>
     </row>
     <row r="37">
@@ -3978,27 +3802,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Restricted cash proceeds from financing</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Total cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F37" s="5" t="n">
+        <v>-1.839902</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.25</v>
+        <v>-2.963994</v>
       </c>
     </row>
     <row r="38">
@@ -4009,17 +3835,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Total cash provided by financing activities</t>
+          <t>Deposits for exploration and evaluation expenditures</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4027,11 +3853,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>4.135052</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>4.626729</v>
+        <v>-0.108892</v>
       </c>
     </row>
     <row r="39">
@@ -4042,25 +3870,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents and restricted cash</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>1.770124</v>
+        <v>-0.525026</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-1.581793</v>
+        <v>-3.092763</v>
       </c>
     </row>
     <row r="40">
@@ -4071,29 +3903,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents and restricted cash, beginning of the year</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Acquisition of Nucleus - transaction costs</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n">
-        <v>1.598575</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G40" s="5" t="n">
-        <v>3.368699</v>
+        <v>-0.042873</v>
       </c>
     </row>
     <row r="41">
@@ -4104,17 +3934,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents and restricted cash, end of the year</t>
+          <t>Total cash used in investing activities</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4123,10 +3953,10 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>3.368699</v>
+        <v>-0.525026</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1.786906</v>
+        <v>-3.244528</v>
       </c>
     </row>
     <row r="42">
@@ -4137,24 +3967,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>0.8186059999999999</v>
+          <t>Shares issued on warrant exercise</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-2.190288</v>
+        <v>0.697112</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4170,27 +3998,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Shares issued for private placement financing</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="n">
-        <v>-0.001902</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>3.55295</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>3.584136</v>
       </c>
     </row>
     <row r="44">
@@ -4201,27 +4027,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Share-based compensation expense</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.586429</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.11501</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.207407</v>
       </c>
     </row>
     <row r="45">
@@ -4232,29 +4060,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Total cash provided by (used in) operating activities</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0.831251</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>-1.839902</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Restricted cash proceeds from financing</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="46">
@@ -4265,27 +4091,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Note receivable</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" s="5" t="n">
-        <v>0.118923</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>4.135052</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>4.626729</v>
       </c>
     </row>
     <row r="47">
@@ -4296,29 +4124,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Total cash (used in) provided by investing activities</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0.118923</v>
+          <t>Change in cash and cash equivalents and restricted cash</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>-0.525026</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.770124</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-1.581793</v>
       </c>
     </row>
     <row r="48">
@@ -4334,22 +4158,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Share issued on warrant exercise</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Cash and cash equivalents and restricted cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.697112</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.598575</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>3.368699</v>
       </c>
     </row>
     <row r="49">
@@ -4365,24 +4191,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Cash and cash equivalents and restricted cash, end of the year</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0.950174</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>1.770124</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.368699</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>1.786906</v>
       </c>
     </row>
     <row r="50">
@@ -4393,24 +4219,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
+          <t>Income (loss) for the year</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.648401</v>
+        <v>0.8186059999999999</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>1.598575</v>
+        <v>-2.190288</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4426,24 +4252,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cash, end of the year</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>1.598575</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>3.368699</v>
+        <v>-0.001902</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4454,139 +4278,149 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Accounting and auditing</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Share-based compensation expense</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.04213</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.188214</v>
+        <v>0.586429</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Total cash provided by (used in) operating activities</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.831251</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.022279</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.482544</v>
+        <v>-1.839902</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Conferences and seminars</t>
+          <t>Note receivable</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E54" s="5" t="n">
+        <v>0.118923</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
-        <v>0.012721</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Director fees 12</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total cash (used in) provided by investing activities</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.118923</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.0639</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.0684</v>
+        <v>-0.525026</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Legal and related</t>
+          <t>Share issued on warrant exercise</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4596,101 +4430,111 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.279176</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.336923</v>
+        <v>0.697112</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Management fees 12</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.950174</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.15435</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.190313</v>
+        <v>1.770124</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Marketing fees</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.648401</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.865658</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>1.647565</v>
+        <v>1.598575</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Travel and related</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of the year</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>1.598575</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.013126</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.166572</v>
+        <v>3.368699</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -4706,24 +4550,18 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounting and auditing</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>0.038445</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.007144</v>
+        <v>0.04213</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.037568</v>
+        <v>0.188214</v>
       </c>
     </row>
     <row r="61">
@@ -4739,24 +4577,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0.042</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.004488</v>
+        <v>0.022279</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.019069</v>
+        <v>0.482544</v>
       </c>
     </row>
     <row r="62">
@@ -4772,7 +4608,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Registration and filing</t>
+          <t>Conferences and seminars</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4781,11 +4617,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>0.122189</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.02121</v>
+        <v>0.012721</v>
       </c>
     </row>
     <row r="63">
@@ -4801,7 +4639,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Director fees 12</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4815,10 +4653,10 @@
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0639</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="64">
@@ -4834,20 +4672,18 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Share-based compensation 11, 12</t>
+          <t>Legal and related</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="5" t="n">
+        <v>0.230385</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.586429</v>
+        <v>0.279176</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.634576</v>
+        <v>0.336923</v>
       </c>
     </row>
     <row r="65">
@@ -4863,7 +4699,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Shareholder communications</t>
+          <t>Management fees 12</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4876,13 +4712,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F65" s="5" t="n">
+        <v>0.15435</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.070257</v>
+        <v>0.190313</v>
       </c>
     </row>
     <row r="66">
@@ -4898,7 +4732,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Transfer agent and shareholder costs</t>
+          <t>Marketing fees</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -4908,10 +4742,10 @@
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.046703</v>
+        <v>0.865658</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.097078</v>
+        <v>1.647565</v>
       </c>
     </row>
     <row r="67">
@@ -4927,24 +4761,18 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Operating loss for the year</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Travel and related</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
+        <v>0.021321</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-2.218072</v>
+        <v>0.013126</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-4.01781</v>
+        <v>0.166572</v>
       </c>
     </row>
     <row r="68">
@@ -4960,24 +4788,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0.003222</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.027784</v>
+        <v>0.007144</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.060522</v>
+        <v>0.037568</v>
       </c>
     </row>
     <row r="69">
@@ -4993,22 +4819,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Recovery of flow through share premium 10</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>-0.004341</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.004488</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.393798</v>
+        <v>0.019069</v>
       </c>
     </row>
     <row r="70">
@@ -5024,22 +4850,18 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 8</t>
+          <t>Registration and filing</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" s="5" t="n">
+        <v>0.020593</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0.122189</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-1.315969</v>
+        <v>0.02121</v>
       </c>
     </row>
     <row r="71">
@@ -5055,24 +4877,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.022574</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-2.190288</v>
+        <v>0.0105</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-4.879459</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row r="72">
@@ -5088,7 +4908,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Share-based compensation 11, 12</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5098,10 +4918,10 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>33.204778</v>
+        <v>0.586429</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>80.786601</v>
+        <v>0.634576</v>
       </c>
     </row>
     <row r="73">
@@ -5117,12 +4937,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Loss per common share – basic and diluted</t>
+          <t>Shareholder communications</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5130,11 +4950,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F73" s="5" t="n">
-        <v>-7e-08</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.070257</v>
       </c>
     </row>
     <row r="74">
@@ -5150,20 +4972,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Total $ 1,584,666 3,552,950 (310,948) (396,234) 5,529,088 697,112 - 105,485 586,429 410,000 (2,190,288) 9,568,260 3,584,136 2,340,000 250,853 (220,007) - (519,486) - 153,500 634,576</t>
+          <t>Transfer agent and shareholder costs</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="5" t="n">
+        <v>0.004441</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>10.912373</v>
+        <v>0.046703</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-4.879459</v>
+        <v>0.097078</v>
       </c>
     </row>
     <row r="75">
@@ -5179,20 +4999,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Deficit $ (3,812,237) - - - - - - - - - (2,190,288) (6,002,525) - - - - - - - - -</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Operating loss for the year</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>-0.691754</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-10.881984</v>
+        <v>-2.218072</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-4.879459</v>
+        <v>-4.01781</v>
       </c>
     </row>
     <row r="76">
@@ -5208,20 +5030,1041 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.027784</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.060522</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Recovery of flow through share premium 10</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.393798</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets 8</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>-1.315969</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>-2.190288</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>-4.879459</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>33.204778</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>80.786601</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Loss per common share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Total $ 1,584,666 3,552,950 (310,948) (396,234) 5,529,088 697,112 - 105,485 586,429 410,000 (2,190,288) 9,568,260 3,584,136 2,340,000 250,853 (220,007) - (519,486) - 153,500 634,576</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>10.912373</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-4.879459</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Deficit $ (3,812,237) - - - - - - - - - (2,190,288) (6,002,525) - - - - - - - - -</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>-10.881984</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>-4.879459</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
           <t>Amount $ 697,112 157,500 - - - - 660,853 (90,053) 472,500 153,500 - - consolidated 4,861,202 3,552,950 (310,948) (396,234) 5,529,088 14,090,670 3,584,136 2,340,000 (220,007)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="n">
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
         <v>20.472113</v>
       </c>
-      <c r="G76" s="5" t="n">
+      <c r="G84" s="5" t="n">
         <v>-0.519486</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Management fees 8</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.28035</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.21825</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Project investigation</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>0.032764</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Share-based compensation 6, 8</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.586429</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Recovery of expenses 1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>0.18899</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Gain on termination of transaction 1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>1.32137</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Net income (loss) and comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Net income (loss) and comprehensive income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>0.8186059999999999</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>-2.190288</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding – basic</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>25.209207</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>33.204778</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding – diluted</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>39.218149</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>33.204778</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Basic income (loss) per common share</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Diluted income (loss) per common share</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>shares     Amount     Reserve        shares          Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Balance December 31, 2022 25,209,207 4,861,202 535,701 -</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" s="5" t="n">
+        <v>0.76606</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-4.630843</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>shares     Amount     Reserve        shares          Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Income for the year Note - - - -</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" s="5" t="n">
+        <v>0.8186059999999999</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0.8186059999999999</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>shares     Amount     Reserve        shares          Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2023 25,209,207 4,861,202 535,701 -</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" s="5" t="n">
+        <v>1.584666</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>-3.812237</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>shares     Amount     Reserve        shares          Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Share issued for cash 6 12,626,862 3,552,950 - -</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" s="5" t="n">
+        <v>3.55295</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>shares     Amount     Reserve        shares          Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Share issue costs - (310,948) - -</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" s="5" t="n">
+        <v>-0.310948</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>shares     Amount     Reserve        shares          Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Flow-through share premium liability - (396,234) - -</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" s="5" t="n">
+        <v>-0.396234</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" s="5" t="n">
+        <v>5.529088</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>13.00375</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>exploration and evaluation asset - -</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>5.529088</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Share issued on exercise of warrants 6 9,958,738 697,112 - -</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>0.697112</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Shares issued for restricted share units 6 500,000 157,500 (157,500) -</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Share-based compensation on option</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Share-based compensation on option issuance - - 586,429 -</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>0.586429</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Share-based compensation on option</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Fair value of finder warrants 6 - - 105,485 -</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="5" t="n">
+        <v>0.105485</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Share-based compensation on option</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Commitment to issue shares 5 - - - 410,000</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Share-based compensation on option</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>-2.190288</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>-2.190288</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Share-based compensation on option</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2024 61,298,557 14,090,670 1,070,115 410,000</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" s="5" t="n">
+        <v>9.56826</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>-6.002525</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
